--- a/doc/PatPet_요구사항정의서.xlsx
+++ b/doc/PatPet_요구사항정의서.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>[PetPulse] 반려동물 AI 건강관리 플랫폼 요구사항 정의서</t>
+          <t>[PatPet] 반려동물 AI 건강관리 플랫폼 요구사항 정의서</t>
         </is>
       </c>
     </row>
